--- a/schedules/2403740/2025-2026-2.xlsx
+++ b/schedules/2403740/2025-2026-2.xlsx
@@ -7,11 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="第16周" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="第17周" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="第18周" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="第19周" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="第20周" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="第1周" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="第2周" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="第3周" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="第4周" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="第5周" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="第6周" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="第7周" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="第8周" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="第9周" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="第10周" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="第11周" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="第12周" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="第13周" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="第14周" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="第15周" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="第16周" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="第17周" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="第18周" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="第19周" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="第20周" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,6 +524,912 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>中华优秀传统文化
+辜秀娟
+1(周)
+修德楼C401</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+10(周)
+A212软件新技术新产品体验实训室</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+10(周)
+A212软件新技术新产品体验实训室</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+10-11(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+10(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+10-11(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+10(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+11(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>形势与政策4
+孔坤杰
+11-14(周)
+励志楼D202数字马院VR虚拟仿真实训室（二）</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+11-12(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+10-11(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+10-11(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>形势与政策4
+孔坤杰
+11-14(周)
+励志楼D202数字马院VR虚拟仿真实训室（二）</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+12(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+11-12(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+12(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
@@ -545,23 +1466,23 @@
 4-5节</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>形势与政策4
+孔坤杰
+11-14(周)
+励志楼D202数字马院VR虚拟仿真实训室（二）</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Spark开发
-杨增春
-16(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>大学生创新创业训练
 向东
-2,4-11,15-18(周)
-育能楼B312</t>
-        </is>
-      </c>
+13,14(周)
+育能楼B318</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>数据分析可视化
@@ -591,10 +1512,10 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Spark开发
-杨增春
-16(周)
-A510大型数据库实训室</t>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
@@ -618,7 +1539,14 @@
 桔园Z103校企合作实训室</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>AI业务流程自动化实战（微专业）
@@ -628,7 +1556,14 @@
         </is>
       </c>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
     </row>
@@ -649,6 +1584,1414 @@
 行知楼2006 AI智能感知与系统集成实训室</t>
         </is>
       </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+13-18(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+14(周)
+A213移动互联网开发实训室</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>形势与政策4
+孔坤杰
+11-14(周)
+励志楼D202数字马院VR虚拟仿真实训室（二）</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+13,14(周)
+育能楼B318</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+14(周)
+A213移动互联网开发实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>中华优秀传统文化
+辜秀娟
+14,15,17,18(周)
+修德楼C401</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+13-18(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+15(周)
+育能楼B320</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>中华优秀传统文化
+辜秀娟
+14,15,17,18(周)
+修德楼C401</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+13-18(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+16(周)
+A510大型数据库实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+17(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+13-18(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+17(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+17(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+17(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>中华优秀传统文化
+辜秀娟
+14,15,17,18(周)
+修德楼C401</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+13-18(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>中华优秀传统文化
+辜秀娟
+14,15,17,18(周)
+修德楼C401</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+14-15,17-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI业务流程自动化实战（微专业）
+熊孟娜
+10-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>AIGC内容创作与智能生成技术（微专业）
+李永
+12-15,17-18(周)
+行知楼2006 AI智能感知与系统集成实训室</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
@@ -740,22 +3083,8 @@
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Spark开发
-杨增春
-17(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>数据预处理技术
-马庆祥
-13-18(周)
-A505 Web前端开发实训室</t>
-        </is>
-      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>数据分析可视化
@@ -775,12 +3104,19 @@
 4-5节</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Spark开发
 杨增春
-17(周)
+2,4-6(周)
 桔园Z103校企合作实训室</t>
         </is>
       </c>
@@ -794,103 +3130,235 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>Spark开发
 杨增春
-17(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>三大节
 6-8节</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>数据仓库综合实训
-杨增春
-8-9,11-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>数据预处理技术
-马庆祥
-14-15,17-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Spark开发
-杨增春
-17(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>中华优秀传统文化
-辜秀娟
-14,15,17,18(周)
-修德楼C401</t>
-        </is>
-      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>四大节
 9-10节</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>数据仓库综合实训
-杨增春
-8-9,11-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>数据预处理技术
-马庆祥
-14-15,17-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>AI业务流程自动化实战（微专业）
-熊孟娜
-10-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>AIGC内容创作与智能生成技术（微专业）
-李永
-12-15,17-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>五大节
@@ -899,23 +3367,9 @@
       </c>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AI业务流程自动化实战（微专业）
-熊孟娜
-10-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>AIGC内容创作与智能生成技术（微专业）
-李永
-12-15,17-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
     </row>
@@ -1006,14 +3460,7 @@
       </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>数据预处理技术
-马庆祥
-13-18(周)
-A505 Web前端开发实训室</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>数据分析可视化
@@ -1033,17 +3480,24 @@
 4-5节</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>大学生创新创业训练
-向东
-2,4-11,15-18(周)
-育能楼B312</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
@@ -1055,32 +3509,18 @@
 6-8节</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>数据仓库综合实训
-杨增春
-8-9,11-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>数据预处理技术
-马庆祥
-14-15,17-18(周)
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
 桔园Z103校企合作实训室</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>中华优秀传统文化
-辜秀娟
-14,15,17,18(周)
-修德楼C401</t>
-        </is>
-      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
     </row>
@@ -1091,43 +3531,22 @@
 9-10节</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>数据仓库综合实训
-杨增春
-8-9,11-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>数据预处理技术
-马庆祥
-14-15,17-18(周)
-桔园Z103校企合作实训室</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>AI业务流程自动化实战（微专业）
-熊孟娜
-10-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>AIGC内容创作与智能生成技术（微专业）
-李永
-12-15,17-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>五大节
@@ -1136,23 +3555,9 @@
       </c>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AI业务流程自动化实战（微专业）
-熊孟娜
-10-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>AIGC内容创作与智能生成技术（微专业）
-李永
-12-15,17-18(周)
-行知楼2006 AI智能感知与系统集成实训室</t>
-        </is>
-      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
     </row>
@@ -1234,7 +3639,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>一大节
@@ -1244,42 +3649,105 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫,蒲梅
+4(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>二大节
 4-5节</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫,蒲梅
+4(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>三大节
 6-8节</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+4(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>四大节
@@ -1287,7 +3755,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -1387,6 +3862,466 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+5(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+5(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+5(周)
+修德楼C409公共计算机实训室四</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+5(周)
+行知楼2001VR虚拟现实教育实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+6(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+6,8(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥,海狄
+6(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
@@ -1402,37 +4337,65 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>二大节
 4-5节</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>三大节
 6-8节</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥,海狄
+7(周)
+修德楼C408公共计算机实训室三</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>四大节
@@ -1440,7 +4403,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -1477,4 +4447,443 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+8-9(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+6,8(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+8(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Spark开发
+杨增春
+2,4-6,8,10(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一大节
+1-3节</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>数据预处理技术
+马庆祥
+8-9(周)
+A505 Web前端开发实训室</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,9-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>二大节
+4-5节</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>体育(4)
+冯志凯
+2-5,7-9,15(周)
+合川运动场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大学生创新创业训练
+向东
+2,4-11,15-18(周)
+育能楼B312</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数据分析可视化
+郭嗣鑫
+2-3,5-6,8-16(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三大节
+6-8节</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>四大节
+9-10节</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数据仓库综合实训
+杨增春
+8-9,11-18(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>数据采集综合实训
+刘莹
+2-7,9,11-13(周)
+桔园Z103校企合作实训室</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>五大节
+11-12节</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>学期:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-2026-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>